--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct/adaptive/max/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct/adaptive/max/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -725,6 +725,265 @@
       <c r="K10" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=1.5,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>92.23999999999999</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>88.03</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>93.41</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=1.5,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>92.08</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>87.91</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>95.52</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.2,scale_th=1.5,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>87.45</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>97.31999999999999</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>95.20999999999999</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.2,scale_th=1.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>92.48</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>50.52</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>88.11</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>95.68000000000001</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>93.54000000000001</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=2.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>87.95999999999999</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>95.61</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>29.79</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=2.5,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>92.16</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>87.98</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>95.59</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>29.42</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=1.4,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>92.06</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>49.93</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>87.91</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>97.66</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>95.55</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>93.29000000000001</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=1.3,type=max</t>
         </is>
       </c>
     </row>

--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct/adaptive/max/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct/adaptive/max/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -984,6 +984,154 @@
       <c r="K17" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=1.3,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>38.77</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>86.92</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>97.17</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>94.94</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>92.48999999999999</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.6,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>91.67</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>50.26</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>87.59</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>97.48999999999999</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>95.36</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>30.37</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>93.03</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=1.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>87.45</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>97.42</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>95.28</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.9,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>91.33</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>50.78</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>87.29000000000001</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>95.18000000000001</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.8,type=max</t>
         </is>
       </c>
     </row>
